--- a/education_forms/045_unpaid_sellers_remedies_quiz--education_forms.xlsx
+++ b/education_forms/045_unpaid_sellers_remedies_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>seller_remedies_quiz</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Sellers Remedies Quiz</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the Sellers Remedies Quiz!</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>product_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quiz_start</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your product?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide product details.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>seller_experiences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What do you do to overcome common selling challenges?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide your experiences.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,12 +601,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>remedies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>What remedies do you use to overcome common selling challenges?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,20 +619,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any additional information about your selling process?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide any additional information.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +646,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>remedies_effectiveness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How effective are the remedies you use?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please rate the effectiveness of your remedies.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,17 +673,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>challenge_overcome</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>Which challenge have you overcome using your remedies?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,15 +701,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>additional_tips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have any additional tips for selling?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide any additional tips.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>remedies_cost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the cost of your remedies?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide the cost.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +750,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>remedies_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How long do you spend on remedies?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide the time.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +782,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>remedies_results</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What results do you get from your remedies?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide results.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +804,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>quiz_end</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Thank you for taking the quiz!</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>You have completed the Sellers Remedies Quiz.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +831,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>additional_questions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you have any additional questions about the quiz?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please ask your questions.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +863,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Can you provide feedback about the quiz?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide feedback.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +890,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Do you have any suggestions for future quizzes?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide suggestions.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +912,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Thank you again for taking the quiz!</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Conclusion.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +939,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>follow_up_questions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Do you have any follow-up questions?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide questions.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,177 +971,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>question2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Do you have any additional comments?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please provide comments.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>question1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>question2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>quiz_end</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1001,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +1029,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>remedies_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>remedies_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>remedies_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>challenge_overcome_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>challenge_overcome_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>challenge_overcome_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>question1_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
